--- a/jira_export_2026-06-25.xlsx
+++ b/jira_export_2026-06-25.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>47,731 €</t>
+          <t>52,031 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -772,14 +772,14 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>15,680 €</t>
+          <t>17,668 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>32,051 €</t>
+          <t>34,363 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -827,7 +827,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>682 h</t>
+          <t>686 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -841,7 +841,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>81.3%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -2273,10 +2273,10 @@
         <v>0</v>
       </c>
       <c r="O21" s="13" t="n">
-        <v>0</v>
+        <v>1331</v>
       </c>
       <c r="P21" s="13" t="n">
-        <v>0</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="22">
@@ -2409,10 +2409,10 @@
         <v>390</v>
       </c>
       <c r="O23" s="17" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="P23" s="13" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
     </row>
     <row r="24">
@@ -3809,7 +3809,7 @@
         <v>1</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>1.75</v>
+        <v>4.75</v>
       </c>
       <c r="L43" s="12" t="inlineStr">
         <is>
@@ -3825,10 +3825,10 @@
         <v>290</v>
       </c>
       <c r="O43" s="13" t="n">
-        <v>290</v>
+        <v>2407</v>
       </c>
       <c r="P43" s="13" t="n">
-        <v>165.71</v>
+        <v>506.74</v>
       </c>
     </row>
     <row r="44">
@@ -5881,10 +5881,10 @@
         <v>910</v>
       </c>
       <c r="O72" s="16" t="n">
-        <v>1228.5</v>
+        <v>1456</v>
       </c>
       <c r="P72" s="16" t="n">
-        <v>158.52</v>
+        <v>187.87</v>
       </c>
     </row>
     <row r="73">
@@ -6953,10 +6953,10 @@
         <v>2400</v>
       </c>
       <c r="O87" s="17" t="n">
-        <v>967.05</v>
+        <v>1396.85</v>
       </c>
       <c r="P87" s="13" t="n">
-        <v>92.09999999999999</v>
+        <v>133.03</v>
       </c>
     </row>
     <row r="88">
@@ -12793,7 +12793,7 @@
         <v>33</v>
       </c>
       <c r="K172" s="15" t="n">
-        <v>15.25</v>
+        <v>16.75</v>
       </c>
       <c r="L172" s="15" t="inlineStr"/>
       <c r="M172" s="15" t="inlineStr"/>
@@ -14049,10 +14049,10 @@
         <v>66535.84</v>
       </c>
       <c r="O195" s="19" t="n">
-        <v>47730.73</v>
+        <v>52031.03</v>
       </c>
       <c r="P195" s="19" t="n">
-        <v>109.98</v>
+        <v>118.65</v>
       </c>
     </row>
   </sheetData>
@@ -15432,13 +15432,13 @@
         <v>239</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>54.75</v>
+        <v>56.25</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>12</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>305.75</v>
+        <v>307.25</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>90.5</v>
@@ -15448,7 +15448,7 @@
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>51.9%</t>
         </is>
       </c>
     </row>
@@ -15459,7 +15459,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>110.5</v>
+        <v>113.5</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>14</v>
@@ -15468,7 +15468,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>125.5</v>
+        <v>128.5</v>
       </c>
       <c r="F6" s="12" t="n">
         <v>15.5</v>
@@ -15478,7 +15478,7 @@
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>47.2%</t>
         </is>
       </c>
     </row>
@@ -15575,16 +15575,16 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>375032</v>
+        <v>370732</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>173358</v>
+        <v>171123</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>201674</v>
+        <v>199609</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>162858</v>
+        <v>160793</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>18605</v>
@@ -15600,10 +15600,10 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>196055</v>
+        <v>194066</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>89306</v>
+        <v>87318</v>
       </c>
       <c r="D6" s="26" t="n">
         <v>106749</v>
@@ -15625,16 +15625,16 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>178977</v>
+        <v>176665</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>84052</v>
+        <v>83805</v>
       </c>
       <c r="D7" s="27" t="n">
-        <v>94925</v>
+        <v>92860</v>
       </c>
       <c r="E7" s="27" t="n">
-        <v>65028</v>
+        <v>62963</v>
       </c>
       <c r="F7" s="27" t="n">
         <v>14535</v>

--- a/jira_export_2026-06-25.xlsx
+++ b/jira_export_2026-06-25.xlsx
@@ -827,7 +827,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>686 h</t>
+          <t>690 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -841,7 +841,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>81.3%</t>
+          <t>81.8%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -4585,7 +4585,7 @@
         <v>1</v>
       </c>
       <c r="K54" s="15" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="L54" s="15" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>130</v>
       </c>
       <c r="P54" s="16" t="n">
-        <v>520</v>
+        <v>173.33</v>
       </c>
     </row>
     <row r="55">
@@ -9989,7 +9989,7 @@
         <v>9</v>
       </c>
       <c r="K130" s="15" t="n">
-        <v>3.38</v>
+        <v>4.12</v>
       </c>
       <c r="L130" s="15" t="inlineStr">
         <is>
@@ -10059,7 +10059,7 @@
         <v>9</v>
       </c>
       <c r="K131" s="12" t="n">
-        <v>3.38</v>
+        <v>4.12</v>
       </c>
       <c r="L131" s="12" t="inlineStr">
         <is>
@@ -12793,7 +12793,7 @@
         <v>33</v>
       </c>
       <c r="K172" s="15" t="n">
-        <v>16.75</v>
+        <v>18.25</v>
       </c>
       <c r="L172" s="15" t="inlineStr"/>
       <c r="M172" s="15" t="inlineStr"/>
@@ -14052,7 +14052,7 @@
         <v>52031.03</v>
       </c>
       <c r="P195" s="19" t="n">
-        <v>118.65</v>
+        <v>117.72</v>
       </c>
     </row>
   </sheetData>
@@ -15429,16 +15429,16 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>239</v>
+        <v>240.5</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>56.25</v>
+        <v>57.75</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>12</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>307.25</v>
+        <v>310.25</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>90.5</v>
@@ -15448,7 +15448,7 @@
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>52.4%</t>
         </is>
       </c>
     </row>
@@ -15459,7 +15459,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>113.5</v>
+        <v>114</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>14</v>
@@ -15468,7 +15468,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>128.5</v>
+        <v>129</v>
       </c>
       <c r="F6" s="12" t="n">
         <v>15.5</v>
@@ -15478,7 +15478,7 @@
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.4%</t>
         </is>
       </c>
     </row>
@@ -15578,10 +15578,10 @@
         <v>370732</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>171123</v>
+        <v>173163</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>199609</v>
+        <v>197569</v>
       </c>
       <c r="E5" s="25" t="n">
         <v>160793</v>
@@ -15590,7 +15590,7 @@
         <v>18605</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>20211</v>
+        <v>18171</v>
       </c>
     </row>
     <row r="6">
@@ -15628,10 +15628,10 @@
         <v>176665</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>83805</v>
+        <v>85845</v>
       </c>
       <c r="D7" s="27" t="n">
-        <v>92860</v>
+        <v>90820</v>
       </c>
       <c r="E7" s="27" t="n">
         <v>62963</v>
@@ -15640,7 +15640,7 @@
         <v>14535</v>
       </c>
       <c r="G7" s="27" t="n">
-        <v>15362</v>
+        <v>13322</v>
       </c>
     </row>
   </sheetData>

--- a/jira_export_2026-06-25.xlsx
+++ b/jira_export_2026-06-25.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>52,031 €</t>
+          <t>54,112 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -772,7 +772,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>17,668 €</t>
+          <t>19,749 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -827,7 +827,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>690 h</t>
+          <t>694 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -841,7 +841,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>82.3%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -6937,7 +6937,7 @@
         <v>4</v>
       </c>
       <c r="K87" s="12" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="L87" s="12" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         <v>1396.85</v>
       </c>
       <c r="P87" s="13" t="n">
-        <v>133.03</v>
+        <v>116.4</v>
       </c>
     </row>
     <row r="88">
@@ -8521,7 +8521,7 @@
         <v>6</v>
       </c>
       <c r="K109" s="12" t="n">
-        <v>3.25</v>
+        <v>4.75</v>
       </c>
       <c r="L109" s="12" t="inlineStr">
         <is>
@@ -10215,10 +10215,10 @@
         <v>6000</v>
       </c>
       <c r="O133" s="17" t="n">
-        <v>0</v>
+        <v>2080.938</v>
       </c>
       <c r="P133" s="13" t="n">
-        <v>0</v>
+        <v>198.18</v>
       </c>
     </row>
     <row r="134">
@@ -11353,7 +11353,7 @@
         <v>15</v>
       </c>
       <c r="K150" s="15" t="n">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="L150" s="15" t="inlineStr">
         <is>
@@ -14049,10 +14049,10 @@
         <v>66535.84</v>
       </c>
       <c r="O195" s="19" t="n">
-        <v>52031.03</v>
+        <v>54111.968</v>
       </c>
       <c r="P195" s="19" t="n">
-        <v>117.72</v>
+        <v>121.4</v>
       </c>
     </row>
   </sheetData>
@@ -15429,7 +15429,7 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>240.5</v>
+        <v>242.75</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>57.75</v>
@@ -15438,17 +15438,17 @@
         <v>12</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>310.25</v>
+        <v>312.5</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>90.5</v>
+        <v>91.5</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>592.2</v>
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.8%</t>
         </is>
       </c>
     </row>
@@ -15459,7 +15459,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>114</v>
+        <v>115.5</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>14</v>
@@ -15468,7 +15468,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>129</v>
+        <v>130.5</v>
       </c>
       <c r="F6" s="12" t="n">
         <v>15.5</v>
@@ -15478,7 +15478,7 @@
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>48.0%</t>
         </is>
       </c>
     </row>
@@ -15575,10 +15575,10 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>370732</v>
+        <v>368651</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>173163</v>
+        <v>171082</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>197569</v>
@@ -15600,10 +15600,10 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>194066</v>
+        <v>191986</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>87318</v>
+        <v>85237</v>
       </c>
       <c r="D6" s="26" t="n">
         <v>106749</v>

--- a/jira_export_2026-06-25.xlsx
+++ b/jira_export_2026-06-25.xlsx
@@ -827,7 +827,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>694 h</t>
+          <t>700 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -841,7 +841,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>82.3%</t>
+          <t>83.0%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -1753,7 +1753,7 @@
         <v>0</v>
       </c>
       <c r="K14" s="15" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="L14" s="15" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>7</v>
       </c>
       <c r="K122" s="15" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="L122" s="15" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         <v>7</v>
       </c>
       <c r="K124" s="15" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="L124" s="15" t="inlineStr">
         <is>
@@ -10199,7 +10199,7 @@
         <v>10</v>
       </c>
       <c r="K133" s="12" t="n">
-        <v>10.5</v>
+        <v>11.75</v>
       </c>
       <c r="L133" s="12" t="inlineStr">
         <is>
@@ -10218,7 +10218,7 @@
         <v>2080.938</v>
       </c>
       <c r="P133" s="13" t="n">
-        <v>198.18</v>
+        <v>177.1</v>
       </c>
     </row>
     <row r="134">
@@ -10957,7 +10957,7 @@
         <v>14</v>
       </c>
       <c r="K144" s="15" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="L144" s="15" t="inlineStr">
         <is>
@@ -10976,7 +10976,7 @@
         <v>250</v>
       </c>
       <c r="P144" s="16" t="n">
-        <v>142.86</v>
+        <v>125</v>
       </c>
     </row>
     <row r="145">
@@ -12669,7 +12669,7 @@
         <v>33</v>
       </c>
       <c r="K170" s="15" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="L170" s="15" t="inlineStr"/>
       <c r="M170" s="15" t="inlineStr"/>
@@ -14052,7 +14052,7 @@
         <v>54111.968</v>
       </c>
       <c r="P195" s="19" t="n">
-        <v>121.4</v>
+        <v>120.45</v>
       </c>
     </row>
   </sheetData>
@@ -15429,7 +15429,7 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>242.75</v>
+        <v>246.25</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>57.75</v>
@@ -15438,7 +15438,7 @@
         <v>12</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>312.5</v>
+        <v>316</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>91.5</v>
@@ -15448,7 +15448,7 @@
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>53.4%</t>
         </is>
       </c>
     </row>
@@ -15490,7 +15490,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>137.25</v>
+        <v>139.5</v>
       </c>
     </row>
   </sheetData>
